--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:06:19+00:00</t>
+    <t>2024-11-07T21:57:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}moped-inv-bund-patient:Eine Ressource die diesem Profil entspricht, darf, außer den in dieser Invariante explizit gewhitelisteten Elementen (inkl. Sub-Elemente) nur den Wert des Ressourcen-Typs 'Patient' beinhalten, welcher mit dieser Expression nicht ausgeschlossen werden kann. {descendants().exclude(Patient.gender | Patient.address.where(extension.url = 'http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode') | Patient.address.extension.where(url = 'http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode') | Patient.address.extension.where(url = 'http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode').descendants() | Patient.resourceType).exists().not()}</t>
   </si>
   <si>
     <t>ClinicalDocument.recordTarget.patientRole</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:57:27+00:00</t>
+    <t>2024-11-07T22:09:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}moped-inv-bund-patient:Eine Ressource die diesem Profil entspricht, darf, außer den in dieser Invariante explizit gewhitelisteten Elementen (inkl. Sub-Elemente) nur den Wert des Ressourcen-Typs 'Patient' beinhalten, welcher mit dieser Expression nicht ausgeschlossen werden kann. {descendants().exclude(Patient.gender | Patient.address.where(extension.url = 'http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode') | Patient.address.extension.where(url = 'http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode') | Patient.address.extension.where(url = 'http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode').descendants() | Patient.resourceType).exists().not()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>ClinicalDocument.recordTarget.patientRole</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-09T09:07:40+00:00</t>
+    <t>2024-11-11T13:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:26:20+00:00</t>
+    <t>2024-11-12T06:42:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:42:28+00:00</t>
+    <t>2024-11-12T07:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:20:07+00:00</t>
+    <t>2024-11-12T07:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:35:41+00:00</t>
+    <t>2024-11-12T07:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:42:03+00:00</t>
+    <t>2024-11-12T08:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:38:00+00:00</t>
+    <t>2024-11-12T08:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:47:06+00:00</t>
+    <t>2024-11-12T20:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T20:06:39+00:00</t>
+    <t>2024-11-14T06:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T06:51:52+00:00</t>
+    <t>2024-11-14T14:31:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:31:22+00:00</t>
+    <t>2024-11-14T14:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:34:15+00:00</t>
+    <t>2024-11-14T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDPatientBundInvariant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:43:46+00:00</t>
+    <t>2024-11-15T18:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
